--- a/Region_results/Region_Forecasting_26_0513_0519.xlsx
+++ b/Region_results/Region_Forecasting_26_0513_0519.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\딜리버스\forecasting_original\Region_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\딜리버스\forecasting_new\Region_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BAEA96-F6A4-492A-A38D-5EC2B95AB3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8468DA4-BACB-40BE-BC3B-BF0C43858105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3962,7 +3962,7 @@
         <v>44</v>
       </c>
       <c r="C239">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="D239">
         <v>321.4716796875</v>
